--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1072.132</v>
+        <v>894.16</v>
       </c>
       <c r="B2">
-        <v>1060.137</v>
+        <v>880.897</v>
       </c>
       <c r="C2">
-        <v>1084.188</v>
+        <v>907.861</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1089.035</v>
+        <v>919.202</v>
       </c>
       <c r="B2">
-        <v>1077.344</v>
+        <v>905.842</v>
       </c>
       <c r="C2">
-        <v>1100.79</v>
+        <v>932.4589999999999</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1159.061</v>
+        <v>1101.009</v>
       </c>
       <c r="B2">
-        <v>1146.998</v>
+        <v>1085.459</v>
       </c>
       <c r="C2">
-        <v>1171.335</v>
+        <v>1116.614</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1168.959</v>
+        <v>1113.016</v>
       </c>
       <c r="B2">
-        <v>1156.621</v>
+        <v>1096.914</v>
       </c>
       <c r="C2">
-        <v>1181.849</v>
+        <v>1128.129</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>894.16</v>
+        <v>829.7569999999999</v>
       </c>
       <c r="B2">
-        <v>880.897</v>
+        <v>816.167</v>
       </c>
       <c r="C2">
-        <v>907.861</v>
+        <v>843.524</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>919.202</v>
+        <v>865.287</v>
       </c>
       <c r="B2">
-        <v>905.842</v>
+        <v>851.992</v>
       </c>
       <c r="C2">
-        <v>932.4589999999999</v>
+        <v>878.574</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1101.009</v>
+        <v>1016.319</v>
       </c>
       <c r="B2">
-        <v>1085.459</v>
+        <v>1000.102</v>
       </c>
       <c r="C2">
-        <v>1116.614</v>
+        <v>1033.545</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1113.016</v>
+        <v>1049.53</v>
       </c>
       <c r="B2">
-        <v>1096.914</v>
+        <v>1032.558</v>
       </c>
       <c r="C2">
-        <v>1128.129</v>
+        <v>1066.42</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>829.7569999999999</v>
+        <v>913.633</v>
       </c>
       <c r="B2">
-        <v>816.167</v>
+        <v>901.534</v>
       </c>
       <c r="C2">
-        <v>843.524</v>
+        <v>925.905</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>865.287</v>
+        <v>939.099</v>
       </c>
       <c r="B2">
-        <v>851.992</v>
+        <v>926.865</v>
       </c>
       <c r="C2">
-        <v>878.574</v>
+        <v>951.13</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1016.319</v>
+        <v>1192.268</v>
       </c>
       <c r="B2">
-        <v>1000.102</v>
+        <v>1176.766</v>
       </c>
       <c r="C2">
-        <v>1033.545</v>
+        <v>1208.217</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1049.53</v>
+        <v>1204.672</v>
       </c>
       <c r="B2">
-        <v>1032.558</v>
+        <v>1188.354</v>
       </c>
       <c r="C2">
-        <v>1066.42</v>
+        <v>1220.627</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>913.633</v>
+        <v>832.898</v>
       </c>
       <c r="B2">
-        <v>901.534</v>
+        <v>821.971</v>
       </c>
       <c r="C2">
-        <v>925.905</v>
+        <v>844.182</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>939.099</v>
+        <v>858.881</v>
       </c>
       <c r="B2">
-        <v>926.865</v>
+        <v>847.448</v>
       </c>
       <c r="C2">
-        <v>951.13</v>
+        <v>869.763</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1192.268</v>
+        <v>1086.327</v>
       </c>
       <c r="B2">
-        <v>1176.766</v>
+        <v>1072.067</v>
       </c>
       <c r="C2">
-        <v>1208.217</v>
+        <v>1101.087</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1204.672</v>
+        <v>1098.927</v>
       </c>
       <c r="B2">
-        <v>1188.354</v>
+        <v>1084.913</v>
       </c>
       <c r="C2">
-        <v>1220.627</v>
+        <v>1113.365</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>832.898</v>
+        <v>1105.735</v>
       </c>
       <c r="B2">
-        <v>821.971</v>
+        <v>1090.344</v>
       </c>
       <c r="C2">
-        <v>844.182</v>
+        <v>1120.878</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>858.881</v>
+        <v>1101.273</v>
       </c>
       <c r="B2">
-        <v>847.448</v>
+        <v>1085.109</v>
       </c>
       <c r="C2">
-        <v>869.763</v>
+        <v>1116.62</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1086.327</v>
+        <v>54617.702</v>
       </c>
       <c r="B2">
-        <v>1072.067</v>
+        <v>51805.285</v>
       </c>
       <c r="C2">
-        <v>1101.087</v>
+        <v>57404.131</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1098.927</v>
+        <v>1412.066</v>
       </c>
       <c r="B2">
-        <v>1084.913</v>
+        <v>1390.848</v>
       </c>
       <c r="C2">
-        <v>1113.365</v>
+        <v>1433.129</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>832.898</v>
+        <v>3944.396</v>
       </c>
       <c r="B2">
-        <v>821.971</v>
+        <v>3889.136</v>
       </c>
       <c r="C2">
-        <v>844.182</v>
+        <v>4001.247</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>858.881</v>
+        <v>3598.473</v>
       </c>
       <c r="B2">
-        <v>847.448</v>
+        <v>3546.557</v>
       </c>
       <c r="C2">
-        <v>869.763</v>
+        <v>3647.878</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1086.327</v>
+        <v>603581.211</v>
       </c>
       <c r="B2">
-        <v>1072.067</v>
+        <v>564688.151</v>
       </c>
       <c r="C2">
-        <v>1101.087</v>
+        <v>643548.443</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1098.927</v>
+        <v>4633.204</v>
       </c>
       <c r="B2">
-        <v>1084.913</v>
+        <v>4561.068</v>
       </c>
       <c r="C2">
-        <v>1113.365</v>
+        <v>4703.991</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_costs_Raw-Boot.xlsx
@@ -376,13 +376,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>3944.396</v>
+        <v>832.898</v>
       </c>
       <c r="B2">
-        <v>3889.136</v>
+        <v>821.971</v>
       </c>
       <c r="C2">
-        <v>4001.247</v>
+        <v>844.182</v>
       </c>
     </row>
   </sheetData>
@@ -414,13 +414,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>3598.473</v>
+        <v>858.881</v>
       </c>
       <c r="B2">
-        <v>3546.557</v>
+        <v>847.448</v>
       </c>
       <c r="C2">
-        <v>3647.878</v>
+        <v>869.763</v>
       </c>
     </row>
   </sheetData>
@@ -452,13 +452,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>603581.211</v>
+        <v>1086.327</v>
       </c>
       <c r="B2">
-        <v>564688.151</v>
+        <v>1072.067</v>
       </c>
       <c r="C2">
-        <v>643548.443</v>
+        <v>1101.087</v>
       </c>
     </row>
   </sheetData>
@@ -490,13 +490,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>4633.204</v>
+        <v>1098.927</v>
       </c>
       <c r="B2">
-        <v>4561.068</v>
+        <v>1084.913</v>
       </c>
       <c r="C2">
-        <v>4703.991</v>
+        <v>1113.365</v>
       </c>
     </row>
   </sheetData>
